--- a/XLibur.Tests/Resource/Other/StyleReferenceFiles/FillAtReservedPosition-MoveFill-Output.xlsx
+++ b/XLibur.Tests/Resource/Other/StyleReferenceFiles/FillAtReservedPosition-MoveFill-Output.xlsx
@@ -428,13 +428,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{E95E88D7-02B3-440F-99C9-880B7EE95A75}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:B1"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
-    <x:col min="1" max="16384" width="9.140625" style="1" customWidth="1"/>
+    <x:col min="1" max="16384" width="9.140625" style="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -442,10 +439,7 @@
       <x:c r="B1" s="4"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed" r:id="rId1"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageSetup orientation="portrait" r:id="rId1"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Other/StyleReferenceFiles/FillAtReservedPosition-MoveFill-Output.xlsx
+++ b/XLibur.Tests/Resource/Other/StyleReferenceFiles/FillAtReservedPosition-MoveFill-Output.xlsx
@@ -431,7 +431,7 @@
   <x:dimension ref="A1:B1"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
-    <x:col min="1" max="16384" width="9.140625" style="1"/>
+    <x:col min="1" max="16384" width="9.144286" style="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2" x14ac:dyDescent="0.25">
